--- a/daily_matches/job_matches_2026-09-18.xlsx
+++ b/daily_matches/job_matches_2026-09-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Software Engineer (Backend) - Essex Management</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hospice of the Valley (AZ)</t>
+          <t>The Emmes Company, LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Azure ML, Synapse, Dataflow, MLflow, Docker, CI/CD</t>
+          <t>RAG, Copilot, S3, BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Git, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7337bb4d468da95</t>
+          <t>https://www.indeed.com/viewjob?jk=49fa2310af8dee52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering</t>
+          <t>Software Engineer III- AI &amp; Engineering/Software as a Service</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git</t>
+          <t>LangChain, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291db07e31423169</t>
+          <t>https://www.indeed.com/viewjob?jk=2a10dde96050d4a0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Snowflake Platform Admin + Data Engineer</t>
+          <t>Software Engineer (Front-End) - Essex Management</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Emmes Company, LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, Glue, Apache Airflow, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7d0eba23d2aa8</t>
+          <t>https://www.indeed.com/viewjob?jk=d569f44c7ed079aa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
+          <t>Software Engineer (Full-Stack) - Essex Management</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>The Emmes Company, LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, BigQuery, Docker, Kubernetes, Snowflake, BigQuery, PostgreSQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c0ea15633322ed</t>
+          <t>https://www.indeed.com/viewjob?jk=1fa0db311b4703de</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist II - ML Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, FastAPI, Docker, Kubernetes, CI/CD, Databricks, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417c64dda2de671d</t>
+          <t>https://www.indeed.com/viewjob?jk=b81902d0763266c3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Wordpress</t>
+          <t>Senior Azure AI Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Clearlink</t>
+          <t>Patient First</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, MySQL, NoSQL, SQL, R</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Synapse, Docker, Kubernetes, AKS, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dd2f17df27cb1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=136815c702b3eaaf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Advisor Data Sciences</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Kubernetes, CI/CD, Terraform, Snowflake, Kafka, PostgreSQL, Python, SQL</t>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Hadoop, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adf012819b158d96</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c089fb737dd2a2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ECPI University</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Hugging Face, PyTorch, Docker, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73ee8bf798535ec7</t>
+          <t>https://www.indeed.com/viewjob?jk=976a9888af4d343c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>AI Developer Co-op - Graduate Program (9 Months)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Church &amp; Dwight Co.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Ewing, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Apache Airflow, CI/CD, Git, Databricks, PySpark, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Git, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f134027d935dcbce</t>
+          <t>https://www.indeed.com/viewjob?jk=6f020f83d0594a82</t>
         </is>
       </c>
     </row>
@@ -788,20 +788,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, Snowflake, Python, SQL, R, Java</t>
+          <t>Copilot, Docker, CI/CD, Git, Snowflake, Databricks, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95a746d2d7d2339a</t>
+          <t>https://www.indeed.com/viewjob?jk=11340d96f177ca10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Research Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL, R</t>
+          <t>Data Lake, CI/CD, Git, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=339e433c61ab096c</t>
+          <t>https://www.indeed.com/viewjob?jk=decc9568d9ed2024</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Research Data Scientist</t>
+          <t>AI Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Pinecone, FastAPI, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e503901d65bdbe12</t>
+          <t>https://www.indeed.com/viewjob?jk=1b96e41fceabf276</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Research Data Scientist</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, Copilot, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a5704c18b25e948</t>
+          <t>https://www.indeed.com/viewjob?jk=e0028de614651c7d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DigiCert</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, MySQL, SQL, R, Java</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b01cd2c5bd8ec60</t>
+          <t>https://www.indeed.com/viewjob?jk=6e01cae988d40726</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Applications Development Senior Programmer Analyst</t>
+          <t>BI Developer - (On-Site)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Coca-Cola Beverages Northeast</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bedford, NH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, XGBoost, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Cortex, Snowflake, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d864c27ecc0f7d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2870b71df6a0d7c9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SCUBI - Software Engineer</t>
+          <t>AWS AgentCore Platform Engineer - 67417</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, AKS, Git, MongoDB, NoSQL, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, CI/CD, Terraform, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a748bd218bc41179</t>
+          <t>https://www.indeed.com/viewjob?jk=932b71737e76ab97</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Analyst - Kiewit Infrastructure Engineers</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Glue, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2aba14c076e6763</t>
+          <t>https://www.indeed.com/viewjob?jk=1733773af2974326</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Agentic AI Solution Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>coras</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Prompt Engineering, Git, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a21049260aa367ea</t>
+          <t>https://www.indeed.com/viewjob?jk=219b8acb0223ed46</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4572 Software Development Engineer III</t>
+          <t>Agentic AI Solution Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Innovaccer</t>
+          <t>coras</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Athena, FastAPI, Docker, Kubernetes, CI/CD, MongoDB, Python, R, Java</t>
+          <t>RAG, Prompt Engineering, Git, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33adb6f5ed20b52</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e186df44978149</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Technology Solutions</t>
+          <t>Sr Software Engineer II, AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>University of Illinois</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Generative AI, RAG, LLaMA, FastAPI, Snowflake, Databricks, Python, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4449e01c5ed9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=f5363a0465dca61d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Data Scientist ll - RiskOS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Aceable</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, AKS, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, XGBoost, Git, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=946f9885537eb383</t>
+          <t>https://www.indeed.com/viewjob?jk=35ad68a536d80759</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Science Co-op - Spring or Summer 2027</t>
+          <t>Data Scientist ll - RiskOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Boston Scientific</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Maple Grove, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, XGBoost, Git, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2553dda50a7c915c</t>
+          <t>https://www.indeed.com/viewjob?jk=21b6bfa1138e9b3f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SDC Camunda developer---Senior-----Raleigh, NC or Dallas, TX</t>
+          <t>Data Scientist ll - RiskOS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, Kafka, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, XGBoost, Git, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3d762b6ff86eed</t>
+          <t>https://www.indeed.com/viewjob?jk=81274a17acb91e85</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer III (Python/React)</t>
+          <t>Data Scientist ll - RiskOS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Git, Kafka, Python, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, XGBoost, Git, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3691ebf6dd4ebf86</t>
+          <t>https://www.indeed.com/viewjob?jk=e6805093b7a80570</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Azure Devops Architect</t>
+          <t>AI Ops Engineer GTM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Agiloft</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, Snowflake, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f773bf1cf3809767</t>
+          <t>https://www.indeed.com/viewjob?jk=3bac92b5345c6267</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS AgentCore Platform Engineer - 67417</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Git, Kafka, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, CI/CD, Terraform, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,637 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4caf38c9fe20311e</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AI Analytics Engineer - Traffic</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>eBay</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>BigQuery, Git, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=651342dc3276ce51</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer - Traffic</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>eBay</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2e71b7fc112852</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Data &amp; AI Consultant</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Lantern</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Generative AI, CI/CD, Databricks, PySpark, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b712ad8b7a8230</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Data &amp; AI Consultant</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Lantern</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Generative AI, CI/CD, Databricks, PySpark, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80e0473d21c9c59f</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior Back End Software Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>EverQuote</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57d64181e7159619</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Sr TA Data Analyst</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Uber</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Git, BigQuery, MySQL, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=716a52ee487c327b</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Optimal Inc.</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, Docker, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f27f8a7550bc36a</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>SR Data Scientist</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>BJ's Wholesale Club</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Marlborough, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Databricks, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=386c5b961e3a3e44</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Wealth Management Tech | Investment Platforms &amp; Systems</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Snowflake, Databricks, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b48f2ccf37551ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Data Engineer III - Python/PySpark/Databricks/AI</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Git, Databricks, PySpark, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=edd604cc148322ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e251dfcac4bfd88</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>JAVA Engineer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b225b911eb75372f</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=31e77034404eb2ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Senior Server Engineer, Data Products</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, Snowflake, Kafka, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fcf8779dc9d8680c</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Associate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Basking Ridge, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=817da6d8953374cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Sr. AI Engineer, Product Devleopment</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Rivian</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Tustin, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Pinecone, CI/CD, Git, Databricks, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85386ce59b6410</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Data Science Intern (Summer 2027)</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Clarios</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Data Lake, Snowflake, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d818405e957e479d</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Senior Healthcare Population Health Data Analyst</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Marsh McLennan Agency</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e2684afdcdfb99f</t>
+          <t>https://www.indeed.com/viewjob?jk=84757f2889a17414</t>
         </is>
       </c>
     </row>
